--- a/新数据生成/#战斗型Boss属性表_3导.xlsx
+++ b/新数据生成/#战斗型Boss属性表_3导.xlsx
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1572</v>
+        <v>1310</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>16.8</v>
@@ -839,7 +839,7 @@
         <v>5.6</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>4.9</v>
@@ -890,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2004.3</v>
+        <v>1670.2</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>14.7</v>
@@ -908,7 +908,7 @@
         <v>6.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="P5" s="4" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="Q5" s="4" t="n">
         <v>4.9</v>
@@ -959,7 +959,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1414.8</v>
+        <v>1179</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>33.7</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="Q6" s="4" t="n">
         <v>4.9</v>
@@ -1028,7 +1028,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>943.2</v>
+        <v>786</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>29.9</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="P7" s="4" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="Q7" s="4" t="n">
         <v>4.9</v>

--- a/新数据生成/#战斗型Boss属性表_3导.xlsx
+++ b/新数据生成/#战斗型Boss属性表_3导.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="战斗型Boss属性" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -129,9 +129,6 @@
     <t>萨哈比精英坦克</t>
   </si>
   <si>
-    <t>森林</t>
-  </si>
-  <si>
     <t>泰森 1</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t>泰森</t>
   </si>
   <si>
-    <t>雪山</t>
-  </si>
-  <si>
     <t>残酷射手 1</t>
   </si>
   <si>
@@ -153,7 +147,31 @@
     <t>残酷射手</t>
   </si>
   <si>
-    <t>草原</t>
+    <t>刘易斯 1</t>
+  </si>
+  <si>
+    <t>刘易斯</t>
+  </si>
+  <si>
+    <t>精射手 1</t>
+  </si>
+  <si>
+    <t>精射手</t>
+  </si>
+  <si>
+    <t>垃圾刺客 1</t>
+  </si>
+  <si>
+    <t>刺客</t>
+  </si>
+  <si>
+    <t>垃圾刺客</t>
+  </si>
+  <si>
+    <t>影流之主 1</t>
+  </si>
+  <si>
+    <t>影流之主</t>
   </si>
 </sst>
 </file>
@@ -548,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -811,7 +829,7 @@
         <v>5.6</v>
       </c>
       <c r="K4" s="2">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -829,10 +847,10 @@
         <v>31</v>
       </c>
       <c r="Q4" s="2">
-        <v>16.367000000000001</v>
+        <v>1.6367</v>
       </c>
       <c r="R4" s="2">
-        <v>4.9100999999999999</v>
+        <v>1.6367</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>32</v>
@@ -879,7 +897,7 @@
         <v>6.3209999999999997</v>
       </c>
       <c r="K5" s="2">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -897,13 +915,13 @@
         <v>35</v>
       </c>
       <c r="Q5" s="2">
-        <v>16.367000000000001</v>
+        <v>1.6367</v>
       </c>
       <c r="R5" s="2">
-        <v>4.9100999999999999</v>
+        <v>1.6367</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="T5" s="2">
         <v>20</v>
@@ -920,7 +938,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2">
         <v>3003</v>
@@ -959,19 +977,19 @@
         <v>29</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="Q6" s="2">
-        <v>16.367000000000001</v>
+        <v>1.6367</v>
       </c>
       <c r="R6" s="2">
-        <v>4.9100999999999999</v>
+        <v>1.6367</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T6" s="2">
         <v>20</v>
@@ -988,7 +1006,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2">
         <v>3004</v>
@@ -1027,19 +1045,19 @@
         <v>29</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q7" s="2">
-        <v>16.367000000000001</v>
+        <v>1.6367</v>
       </c>
       <c r="R7" s="2">
-        <v>4.9100999999999999</v>
+        <v>1.6367</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="T7" s="2">
         <v>20</v>
@@ -1051,6 +1069,278 @@
         <v>10</v>
       </c>
       <c r="W7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3005</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1200</v>
+      </c>
+      <c r="F8" s="2">
+        <v>33.6</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>198.4</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="2">
+        <v>20</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.67310000000000003</v>
+      </c>
+      <c r="V8" s="2">
+        <v>10</v>
+      </c>
+      <c r="W8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3006</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>900</v>
+      </c>
+      <c r="F9" s="2">
+        <v>48</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>235.6</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="2">
+        <v>20</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.79930000000000001</v>
+      </c>
+      <c r="V9" s="2">
+        <v>10</v>
+      </c>
+      <c r="W9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3007</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>700</v>
+      </c>
+      <c r="F10" s="2">
+        <v>45</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>15</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>175</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" s="2">
+        <v>20</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.59370000000000001</v>
+      </c>
+      <c r="V10" s="2">
+        <v>10</v>
+      </c>
+      <c r="W10" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3008</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>900</v>
+      </c>
+      <c r="F11" s="2">
+        <v>48</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J11" s="2">
+        <v>16</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>202</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="2">
+        <v>20</v>
+      </c>
+      <c r="U11" s="2">
+        <v>1.028</v>
+      </c>
+      <c r="V11" s="2">
+        <v>10</v>
+      </c>
+      <c r="W11" s="2">
         <v>3</v>
       </c>
     </row>
